--- a/utils/monday_sprint_sprint_2026-12.xlsx
+++ b/utils/monday_sprint_sprint_2026-12.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="388">
   <si>
     <t>Ticket</t>
   </si>
@@ -117,6 +117,9 @@
     <t>10/02/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -177,645 +180,633 @@
     <t>Alteração de registro de pintura</t>
   </si>
   <si>
-    <t>Sistema de registro de pintura: Teria como o Log aparecer de uma forma parecida com essa descrição? ( Cadastro de quem alterou), (Descrição do que foi alterado Ex. Alterado medição da camada Top Coat com tolerância: Min.: ........., Max.: .........., Medição anterior: ............, Alterado para: ..</t>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>32079</t>
+  </si>
+  <si>
+    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
+  </si>
+  <si>
+    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>04/06/2025</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>37623</t>
+  </si>
+  <si>
+    <t>Melhoria - Restrição de preenchimento</t>
+  </si>
+  <si>
+    <t>Boa tarde, Sandro, Gentileza criar a restrição no campo Data Entrega, que em caso do CFOP for inicial com 7, não permitir o preenchimento, ou apagar a informação. Está sendo incluso informações errôneas.</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>37461</t>
+  </si>
+  <si>
+    <t>Altona || Adiantamento de Clientes do Exterior - Relatório de Variação Cambial - (Reunião) (copy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solicito a criação de uma rotina e posteriormente de um relatório que faça a demonstração da variação cambial dos adiantamentos de clientes do exterior. Para isso é preciso: 1) Criar um campo para cadastrar a moeda e sua respectiva cotação. Essa cotação será alimentada manualmente. Exemplo: Dólar – </t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>37298</t>
+  </si>
+  <si>
+    <t>Melhoria | Custo de venda Orçamento Nacional (REUNIÃO)</t>
+  </si>
+  <si>
+    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>37530</t>
+  </si>
+  <si>
+    <t>Layout ofertas exportação</t>
+  </si>
+  <si>
+    <t>Visualizar todos os seus componentes (MRP) e quantidade consumida</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Teste de nova Versão</t>
+  </si>
+  <si>
+    <t>35602</t>
+  </si>
+  <si>
+    <t>Coleta e identificação de sequencia - Analise de multiplas Fotos</t>
+  </si>
+  <si>
+    <t>37256</t>
+  </si>
+  <si>
+    <t>Melhoria no sistema de ACR</t>
+  </si>
+  <si>
+    <t>Bom dia, Chamado para implementarmos melhorias no sistema de ACR. 1. Anexar análises de causa raiz junto aos pré formulários. 2. Identificar o tipo de gatilho no pré formulário 3. Melhorar resolução da tela de lista de causa raíz (está muito pequena) 4. Melhorar interface e interações para o usuário</t>
+  </si>
+  <si>
+    <t>Enzo Luiz Okabe Auad</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>12/05/2026</t>
+  </si>
+  <si>
+    <t>19909</t>
+  </si>
+  <si>
+    <t>Criar KB Genexus especifica para Registro de pinturas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Visando uma melhoria no setor de pintura e uma adequação para ISO9001, o registro de pintura é hoje realizado manualmente pelo pintor, correndo assim, o risco do mesmo esquecer de preencher o documento ao final da atividade. A ideia seria inserir um registro digital, parecido com o que é </t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>25/04/2023</t>
+  </si>
+  <si>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>36541</t>
+  </si>
+  <si>
+    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
+  </si>
+  <si>
+    <t>36816</t>
+  </si>
+  <si>
+    <t>Gráfico de barras empilhadas “reprovação ao longo dos meses”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde! Favor elaborar uma página de BI para acompanhamento dos ensaios mecânicos. Esta página deve ser anexa ao sistema já existente "Resultados Metalúrgico" dentro da aba "Qualidade". Anexo, uma descrição de como deve ser esta página. Sugiro que leiam o documento por completo e então marcarmos </t>
+  </si>
+  <si>
+    <t>Andre Gustavo Scharf</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>35764</t>
+  </si>
+  <si>
+    <t>Tela de Matrículas / Participantes</t>
+  </si>
+  <si>
+    <t>CRIAÇÃO DE B.I. PARA ACOMPANHAMENTO DE RESULTADOS DE ENSAIOS MECÂNICO</t>
+  </si>
+  <si>
+    <t>36219</t>
+  </si>
+  <si>
+    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
+  </si>
+  <si>
+    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>23/01/2026</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>37751</t>
+  </si>
+  <si>
+    <t>Melhoria no modulo de estorno para item de estoque</t>
+  </si>
+  <si>
+    <t>Boa tarde! Atualmente, o processo de estorno de itens de estoque é trabalhoso, pois exige várias etapas para sua execução. Diante disso, solicitamos a disponibilização, dentro do WMS do Almoxarifado, de um processo unificado de estorno, no qual o colaborador possa: Informar o código do item a ser es</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>37526</t>
+  </si>
+  <si>
+    <t>PDI - Relatório de apontamentos</t>
+  </si>
+  <si>
+    <t>Verificar a situação apresentada pelo usuário Gerson Mendonça: Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Alexandre Longo</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
+    <t>23839</t>
+  </si>
+  <si>
+    <t>Sistema de Separação Part 1/2</t>
+  </si>
+  <si>
+    <t>37575</t>
+  </si>
+  <si>
+    <t>ADICIONAR NO APONTAMENTO DIGITAL - 279 - RETRABALHO DE ESMERIL APÓS VISUAL.</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito adicionar a opção no apontamento digital, conforme sugestão abaixo; Operação - Descrição da Operação. 279 - RETRABALHO DE ESMERIL APÓS VISUAL. MOTIVO: Os ajustadores precisam RETRABALHAR algumas áreas que o inspetor da qualidade julga não conforme. At.te,</t>
+  </si>
+  <si>
+    <t>Juliano Carriel</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>37746</t>
+  </si>
+  <si>
+    <t>Altona || Consignados - Diferença nos saldos</t>
+  </si>
+  <si>
+    <t>Sandro! O estoque de consignados ainda não fecha, perceba na comparação que eu fiz. Nela eu conferi entradas e consumo no Benner e no SNB, mas os saldos finais são diferentes. De onde eu tirei o saldo de R$ 521.678,11. Usando teu relatório e excluindo alguns grupos que não devem estar ali: Podes ver</t>
+  </si>
+  <si>
+    <t>37129</t>
+  </si>
+  <si>
+    <t>Em ambos os alertas das implementações 1 e 2 devem ser gerados relatórios mensais para cada implementação,</t>
+  </si>
+  <si>
+    <t>Bom dia, Chamado Prioritário para correção de não conformidade identificada durante auditoria terceirizada não oficial da ISO 9001. Recentemente foi feita uma alteração no sistema na qual as ordens preventivas ao checar na caixa ilustrada abaixo sejam abertas como uma SS (solicitação de serviço) com</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>37466</t>
+  </si>
+  <si>
+    <t>Calibração de Maquinas de Solda</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos de uma alteração no sistema de manutenção, com relação a baixa de OS para maquinas de solda (família 9). Precisamos que seja feito uma automação, para quando o mantenedor selecione o defeito do equipamento no momento do apontamento, alguns defeitos permitam que a OS seja encerrad</t>
+  </si>
+  <si>
+    <t>Luiz Henrique Rocha Junior</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>36063</t>
+  </si>
+  <si>
+    <t>Liberação Ensaio Mecanico Automatico</t>
+  </si>
+  <si>
+    <t>23838</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
+  </si>
+  <si>
+    <t>37499</t>
+  </si>
+  <si>
+    <t>Alteração sistema registro USE-ULE Windows</t>
+  </si>
+  <si>
+    <t>Bom dia, Necessitamos que seja feita uma alteração no sistema de registro USE-ULE, precisamos que as imagens que ficam anexas as perguntas, quando exibidas pelo relatório do botão "Imprime Registro" sejam de um tamanho maior, que seja possível analisar de forma clara pelo computador. Sugerimos que s</t>
+  </si>
+  <si>
+    <t>João Eduardo Zarth</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>Gráfico de barras empilhadas “Retrabalhos para aprovação”</t>
+  </si>
+  <si>
+    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada</t>
+  </si>
+  <si>
+    <t>Tela apoio para forçar envio de dados.</t>
+  </si>
+  <si>
+    <t>37230</t>
+  </si>
+  <si>
+    <t>Melhoria SMI - Solicitação da supervisão - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>36641</t>
+  </si>
+  <si>
+    <t>Sequencial number Clientes</t>
+  </si>
+  <si>
+    <t>Gráficos de “acompanhamento LE” e “Acompanhamento LR”</t>
+  </si>
+  <si>
+    <t>37300</t>
+  </si>
+  <si>
+    <t>AVISO DE SETORES COM CHECKLIST E/OU FORMULÁRIO EM ABERTO E SALDO JÁ MOVIMENTADO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor criar um aviso semanal por e-mail dos setores que possuem checklists e/ou formulários em aberto (Não) e que estejam com a quantidade despachada igual a quantidade programada. Esse aviso deve ser via outlook para o e-mail arquivo@altona.com.br, no PDF anexo deve conter sequência e quai</t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy) (copy) (copy)</t>
+  </si>
+  <si>
+    <t>35727</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Erro Planilhão - Itens conjuntos</t>
+  </si>
+  <si>
+    <t>Boa tarde Pela primeira vez na UPR, teremos um item de fundido que atenderá a dois conjuntos diferentes. Atualmente, temos 13 peças do fundido em processo e 4 peças dos conjuntos em depósito. No entanto, o Planilhão está considerando apenas 1 peça em estoque, não reconhecendo as outras 3. É importan</t>
+  </si>
+  <si>
+    <t>Taynara Frare</t>
+  </si>
+  <si>
+    <t>15/12/2025</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>37446</t>
+  </si>
+  <si>
+    <t>PAINEL DE VISUALIZAÇÃO PARA LINHAS UPR</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicitamos a elaboração de um painel de visualização para as linhas UPR, estruturado nos mesmos padrões utilizados para os painéis de jato e manipuladores, com o objetivo de aprimorar o acompanhamento por parte da liderança. A disposição;</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>32150</t>
+  </si>
+  <si>
+    <t>Inventario WMS - Registro de Ajuste de Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>06/06/2025</t>
+  </si>
+  <si>
+    <t>37169</t>
+  </si>
+  <si>
+    <t>Alteração em relatorio dentro do sistema "Apontamento de produção"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, solicito a alteração no relatório de apontamento por funcionário quando "gerar o Excel". Preciso que no relatório saia o turno e o setor que cada funcionário faz parte ( inspeção END ou DIM). Motivo: Facilitar e otimizar o tempo de elaboração do relatório disponibilizado para liderança e </t>
+  </si>
+  <si>
+    <t>Gerson Mendonça</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>Consulta geral de OPs - Dataviews</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>37095</t>
+  </si>
+  <si>
+    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
+  </si>
+  <si>
+    <t>Rodrigo Santos Rocha</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>36232</t>
+  </si>
+  <si>
+    <t>Report técnico - Acompanhamento - Homologação</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>Gráfico pizza “reprova relativa semanal”</t>
+  </si>
+  <si>
+    <t>Atualizar campos: data, hora e prazo da proposta</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>25310</t>
+  </si>
+  <si>
+    <t>Sistema de Controle de Orçamento de Entregas de Venda</t>
+  </si>
+  <si>
+    <t>Boa Tarde Segue anexo escopo para criação do sistema de controle de orçamentos de Entrega de venda, para comparação com o realizado e provisionamento de custo para a controladoria.</t>
+  </si>
+  <si>
+    <t>26/03/2024</t>
+  </si>
+  <si>
+    <t>Visualização completa dos Dados da OP</t>
+  </si>
+  <si>
+    <t>Consulta geral de OPs (filtro por datas, modelo, sequencia, situação)</t>
+  </si>
+  <si>
+    <t>37781</t>
+  </si>
+  <si>
+    <t>Controle de sequência por nota fiscal - Alerta notas fiscais sem sequencia informada</t>
+  </si>
+  <si>
+    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
+  </si>
+  <si>
+    <t>36624</t>
+  </si>
+  <si>
+    <t>Problema</t>
+  </si>
+  <si>
+    <t>Indicadores de retrabalho</t>
+  </si>
+  <si>
+    <t>Bom dia. Foi percebido diferen?as entre gr?ficos e dados nos indicadores abaixo. Favor verificar. No exemplo, foi filtrado os setores da KOMATSU. Selecionado o top 3 modelos com maior n?mero de horas em retrabalho. Ao extrair o excel, o total de horas ultrapassa significativamente a quantidade de ho</t>
+  </si>
+  <si>
+    <t>Bruno da Silva</t>
+  </si>
+  <si>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>29848</t>
+  </si>
+  <si>
+    <t>Alteração da referência de Etiqueta para Romaneio - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Preparar Ambiente</t>
+  </si>
+  <si>
+    <t>36403</t>
+  </si>
+  <si>
+    <t>Informação desmoldagem incompleta - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Boa tarde, Informação do segundo tempo de desmoldagem não está aparecendo no email de desmoldagem conforme informação da OTF. Att.</t>
+  </si>
+  <si>
+    <t>Darlan Pressi</t>
+  </si>
+  <si>
+    <t>02/02/2026</t>
+  </si>
+  <si>
+    <t>36055</t>
+  </si>
+  <si>
+    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER</t>
+  </si>
+  <si>
+    <t>37394</t>
+  </si>
+  <si>
+    <t>Rateio Jato Dirigido 1 e 2 - Fazer QG para atualizar operações na apon3 com base no estado da peça (copy)</t>
+  </si>
+  <si>
+    <t>Boa tarde, Hoje (20/03/26 ) foi criado as operações jato dirigido para cadastrarmos os tempos na CPP para rateio de tempo Qlik. Precisamos que esse rateio seja retroativo. No apontamento eletrônico o estado da peça era somente apontado para informação e não apontado sua real operação. Precisamos que</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>36808</t>
+  </si>
+  <si>
+    <t>Melhorias setor 596</t>
+  </si>
+  <si>
+    <t>Bom dia, Gostaria de solicitar as seguintes melhorias no setor 596. 1 - Não deve ser possível movimentar o setor 596 caso tenha alguma pergunta ou item do formulário em aberto, conforme já é feito pra outros setores. 2 - Movimentação do 596 - para os fluxos 100, 102, 103 e 108 no momento da moviment</t>
+  </si>
+  <si>
+    <t>Paula Rosa M. Grando</t>
+  </si>
+  <si>
+    <t>Implementar Alerta de Solicitações de serviço com status de aguardando programação</t>
+  </si>
+  <si>
+    <t>Envio de ofertar trocar o usuário responsável</t>
+  </si>
+  <si>
+    <t>37160</t>
+  </si>
+  <si>
+    <t>Conversão da KB comercial para Gx18</t>
+  </si>
+  <si>
+    <t>Prezados, Precisamos migrar a aplicação do comercial, atualmente na versão gx75 para a versão 18. Principais entregas: - Levantar funcionalidades usadas e necessárias para a migração - Desenhar fluxo de trabalho com aplicação web - Converter objetos Atenciosamente,</t>
+  </si>
+  <si>
+    <t>36632</t>
+  </si>
+  <si>
+    <t>Multiplos de Caixa de ferro</t>
+  </si>
+  <si>
+    <t>Bom dia! Gostaria de criar um campo no ERP para cadastro de quantidade de peças por transferência (lote de transferência) Ex: Tipo de equipamento e Quantidade 1. Caixas de ferro: XX peças do modelo YYYYYY 2. Racks Stara: XX peças do modelo AAAAAA 3. Pallets: XX peças do modelo BBBBB Quem terá acesso</t>
+  </si>
+  <si>
+    <t>36206</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
+  </si>
+  <si>
+    <t>37412</t>
+  </si>
+  <si>
+    <t>Registro de Preset</t>
+  </si>
+  <si>
+    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
   </si>
   <si>
     <t>Lucas Sebold Movidesk</t>
   </si>
   <si>
-    <t>18/02/2026</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>32079</t>
-  </si>
-  <si>
-    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>04/06/2025</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>37623</t>
-  </si>
-  <si>
-    <t>Melhoria - Restrição de preenchimento</t>
-  </si>
-  <si>
-    <t>Boa tarde, Sandro, Gentileza criar a restrição no campo Data Entrega, que em caso do CFOP for inicial com 7, não permitir o preenchimento, ou apagar a informação. Está sendo incluso informações errôneas.</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>01/04/2026</t>
-  </si>
-  <si>
-    <t>12/05/2026</t>
-  </si>
-  <si>
-    <t>37461</t>
-  </si>
-  <si>
-    <t>Altona || Adiantamento de Clientes do Exterior - Relatório de Variação Cambial - (Reunião) (copy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solicito a criação de uma rotina e posteriormente de um relatório que faça a demonstração da variação cambial dos adiantamentos de clientes do exterior. Para isso é preciso: 1) Criar um campo para cadastrar a moeda e sua respectiva cotação. Essa cotação será alimentada manualmente. Exemplo: Dólar – </t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>37298</t>
-  </si>
-  <si>
-    <t>Melhoria | Custo de venda Orçamento Nacional (REUNIÃO)</t>
-  </si>
-  <si>
-    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
-  </si>
-  <si>
-    <t>37530</t>
-  </si>
-  <si>
-    <t>Layout ofertas exportação</t>
-  </si>
-  <si>
-    <t>Visualizar todos os seus componentes (MRP) e quantidade consumida</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Teste de nova Versão</t>
-  </si>
-  <si>
-    <t>35602</t>
-  </si>
-  <si>
-    <t>Coleta e identificação de sequencia - Analise de multiplas Fotos</t>
-  </si>
-  <si>
-    <t>37256</t>
-  </si>
-  <si>
-    <t>Melhoria no sistema de ACR</t>
-  </si>
-  <si>
-    <t>Bom dia, Chamado para implementarmos melhorias no sistema de ACR. 1. Anexar análises de causa raiz junto aos pré formulários. 2. Identificar o tipo de gatilho no pré formulário 3. Melhorar resolução da tela de lista de causa raíz (está muito pequena) 4. Melhorar interface e interações para o usuário</t>
-  </si>
-  <si>
-    <t>Enzo Luiz Okabe Auad</t>
-  </si>
-  <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
-    <t>17/05/2026</t>
-  </si>
-  <si>
-    <t>19909</t>
-  </si>
-  <si>
-    <t>Criar KB Genexus especifica para Registro de pinturas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Visando uma melhoria no setor de pintura e uma adequação para ISO9001, o registro de pintura é hoje realizado manualmente pelo pintor, correndo assim, o risco do mesmo esquecer de preencher o documento ao final da atividade. A ideia seria inserir um registro digital, parecido com o que é </t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>25/04/2023</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>36541</t>
-  </si>
-  <si>
-    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
-  </si>
-  <si>
-    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
-  </si>
-  <si>
-    <t>Alini Ferreira Ganda</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
-    <t>36816</t>
-  </si>
-  <si>
-    <t>Gráfico de barras empilhadas “reprovação ao longo dos meses”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde! Favor elaborar uma página de BI para acompanhamento dos ensaios mecânicos. Esta página deve ser anexa ao sistema já existente "Resultados Metalúrgico" dentro da aba "Qualidade". Anexo, uma descrição de como deve ser esta página. Sugiro que leiam o documento por completo e então marcarmos </t>
-  </si>
-  <si>
-    <t>Andre Gustavo Scharf</t>
-  </si>
-  <si>
-    <t>35764</t>
-  </si>
-  <si>
-    <t>Tela de Matrículas / Participantes</t>
-  </si>
-  <si>
-    <t>CRIAÇÃO DE B.I. PARA ACOMPANHAMENTO DE RESULTADOS DE ENSAIOS MECÂNICO</t>
-  </si>
-  <si>
-    <t>36219</t>
-  </si>
-  <si>
-    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
-  </si>
-  <si>
-    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>37751</t>
-  </si>
-  <si>
-    <t>Melhoria no modulo de estorno para item de estoque</t>
-  </si>
-  <si>
-    <t>Boa tarde! Atualmente, o processo de estorno de itens de estoque é trabalhoso, pois exige várias etapas para sua execução. Diante disso, solicitamos a disponibilização, dentro do WMS do Almoxarifado, de um processo unificado de estorno, no qual o colaborador possa: Informar o código do item a ser es</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>08/04/2026</t>
-  </si>
-  <si>
-    <t>37526</t>
-  </si>
-  <si>
-    <t>PDI - Relatório de apontamentos</t>
-  </si>
-  <si>
-    <t>Verificar a situação apresentada pelo usuário Gerson Mendonça: Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Alexandre Longo</t>
-  </si>
-  <si>
-    <t>27/03/2026</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>23839</t>
-  </si>
-  <si>
-    <t>Sistema de Separação Part 1/2</t>
-  </si>
-  <si>
-    <t>37575</t>
-  </si>
-  <si>
-    <t>ADICIONAR NO APONTAMENTO DIGITAL - 279 - RETRABALHO DE ESMERIL APÓS VISUAL.</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito adicionar a opção no apontamento digital, conforme sugestão abaixo; Operação - Descrição da Operação. 279 - RETRABALHO DE ESMERIL APÓS VISUAL. MOTIVO: Os ajustadores precisam RETRABALHAR algumas áreas que o inspetor da qualidade julga não conforme. At.te,</t>
-  </si>
-  <si>
-    <t>Juliano Carriel</t>
-  </si>
-  <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>37746</t>
-  </si>
-  <si>
-    <t>Altona || Consignados - Diferença nos saldos</t>
-  </si>
-  <si>
-    <t>Sandro! O estoque de consignados ainda não fecha, perceba na comparação que eu fiz. Nela eu conferi entradas e consumo no Benner e no SNB, mas os saldos finais são diferentes. De onde eu tirei o saldo de R$ 521.678,11. Usando teu relatório e excluindo alguns grupos que não devem estar ali: Podes ver</t>
-  </si>
-  <si>
-    <t>37129</t>
-  </si>
-  <si>
-    <t>Em ambos os alertas das implementações 1 e 2 devem ser gerados relatórios mensais para cada implementação,</t>
-  </si>
-  <si>
-    <t>Bom dia, Chamado Prioritário para correção de não conformidade identificada durante auditoria terceirizada não oficial da ISO 9001. Recentemente foi feita uma alteração no sistema na qual as ordens preventivas ao checar na caixa ilustrada abaixo sejam abertas como uma SS (solicitação de serviço) com</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>37466</t>
-  </si>
-  <si>
-    <t>Calibração de Maquinas de Solda</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos de uma alteração no sistema de manutenção, com relação a baixa de OS para maquinas de solda (família 9). Precisamos que seja feito uma automação, para quando o mantenedor selecione o defeito do equipamento no momento do apontamento, alguns defeitos permitam que a OS seja encerrad</t>
-  </si>
-  <si>
-    <t>Luiz Henrique Rocha Junior</t>
-  </si>
-  <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
-    <t>36063</t>
-  </si>
-  <si>
-    <t>Liberação Ensaio Mecanico Automatico</t>
-  </si>
-  <si>
-    <t>23838</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
-  </si>
-  <si>
-    <t>37499</t>
-  </si>
-  <si>
-    <t>Alteração sistema registro USE-ULE Windows</t>
-  </si>
-  <si>
-    <t>Bom dia, Necessitamos que seja feita uma alteração no sistema de registro USE-ULE, precisamos que as imagens que ficam anexas as perguntas, quando exibidas pelo relatório do botão "Imprime Registro" sejam de um tamanho maior, que seja possível analisar de forma clara pelo computador. Sugerimos que s</t>
-  </si>
-  <si>
-    <t>João Eduardo Zarth</t>
-  </si>
-  <si>
-    <t>26/03/2026</t>
-  </si>
-  <si>
-    <t>Gráfico de barras empilhadas “Retrabalhos para aprovação”</t>
-  </si>
-  <si>
-    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada</t>
-  </si>
-  <si>
-    <t>Tela apoio para forçar envio de dados.</t>
-  </si>
-  <si>
-    <t>37230</t>
-  </si>
-  <si>
-    <t>Melhoria SMI - Solicitação da supervisão - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
-  </si>
-  <si>
-    <t>13/03/2026</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>36641</t>
-  </si>
-  <si>
-    <t>Sequencial number Clientes</t>
-  </si>
-  <si>
-    <t>Boa tarde, Conforme conversado com o Sr. Flavio, precisamos criar uma regrar referente aos clientes da Altona que necessitam de um serial number fora a parte, que anda em paralelo da sequência da peça, um exemplo é a Solar Turbines. Esse "lot number" é criado no momento da programação da sequência q</t>
-  </si>
-  <si>
-    <t>Jackson Souza</t>
-  </si>
-  <si>
-    <t>12/02/2026</t>
-  </si>
-  <si>
-    <t>Gráficos de “acompanhamento LE” e “Acompanhamento LR”</t>
-  </si>
-  <si>
-    <t>37300</t>
-  </si>
-  <si>
-    <t>AVISO DE SETORES COM CHECKLIST E/OU FORMULÁRIO EM ABERTO E SALDO JÁ MOVIMENTADO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor criar um aviso semanal por e-mail dos setores que possuem checklists e/ou formulários em aberto (Não) e que estejam com a quantidade despachada igual a quantidade programada. Esse aviso deve ser via outlook para o e-mail arquivo@altona.com.br, no PDF anexo deve conter sequência e quai</t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy) (copy) (copy)</t>
-  </si>
-  <si>
-    <t>35727</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Erro Planilhão - Itens conjuntos</t>
-  </si>
-  <si>
-    <t>Boa tarde Pela primeira vez na UPR, teremos um item de fundido que atenderá a dois conjuntos diferentes. Atualmente, temos 13 peças do fundido em processo e 4 peças dos conjuntos em depósito. No entanto, o Planilhão está considerando apenas 1 peça em estoque, não reconhecendo as outras 3. É importan</t>
-  </si>
-  <si>
-    <t>Taynara Frare</t>
-  </si>
-  <si>
-    <t>15/12/2025</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>37446</t>
-  </si>
-  <si>
-    <t>PAINEL DE VISUALIZAÇÃO PARA LINHAS UPR</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicitamos a elaboração de um painel de visualização para as linhas UPR, estruturado nos mesmos padrões utilizados para os painéis de jato e manipuladores, com o objetivo de aprimorar o acompanhamento por parte da liderança. A disposição;</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>32150</t>
-  </si>
-  <si>
-    <t>Inventario WMS - Registro de Ajuste de Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>06/06/2025</t>
-  </si>
-  <si>
-    <t>37169</t>
-  </si>
-  <si>
-    <t>Alteração em relatorio dentro do sistema "Apontamento de produção"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, solicito a alteração no relatório de apontamento por funcionário quando "gerar o Excel". Preciso que no relatório saia o turno e o setor que cada funcionário faz parte ( inspeção END ou DIM). Motivo: Facilitar e otimizar o tempo de elaboração do relatório disponibilizado para liderança e </t>
-  </si>
-  <si>
-    <t>Gerson Mendonça</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>Consulta geral de OPs - Dataviews</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>37095</t>
-  </si>
-  <si>
-    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
-  </si>
-  <si>
-    <t>Rodrigo Santos Rocha</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>36232</t>
-  </si>
-  <si>
-    <t>Report técnico - Acompanhamento - Homologação</t>
-  </si>
-  <si>
-    <t>Gráfico pizza “reprova relativa semanal”</t>
-  </si>
-  <si>
-    <t>Atualizar campos: data, hora e prazo da proposta</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>25310</t>
-  </si>
-  <si>
-    <t>Sistema de Controle de Orçamento de Entregas de Venda</t>
-  </si>
-  <si>
-    <t>Boa Tarde Segue anexo escopo para criação do sistema de controle de orçamentos de Entrega de venda, para comparação com o realizado e provisionamento de custo para a controladoria.</t>
-  </si>
-  <si>
-    <t>26/03/2024</t>
-  </si>
-  <si>
-    <t>Visualização completa dos Dados da OP</t>
-  </si>
-  <si>
-    <t>Consulta geral de OPs (filtro por datas, modelo, sequencia, situação)</t>
-  </si>
-  <si>
-    <t>37781</t>
-  </si>
-  <si>
-    <t>Controle de sequência por nota fiscal - Alerta notas fiscais sem sequencia informada</t>
-  </si>
-  <si>
-    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
-  </si>
-  <si>
-    <t>36624</t>
-  </si>
-  <si>
-    <t>Problema</t>
-  </si>
-  <si>
-    <t>Indicadores de retrabalho</t>
-  </si>
-  <si>
-    <t>Bom dia. Foi percebido diferen?as entre gr?ficos e dados nos indicadores abaixo. Favor verificar. No exemplo, foi filtrado os setores da KOMATSU. Selecionado o top 3 modelos com maior n?mero de horas em retrabalho. Ao extrair o excel, o total de horas ultrapassa significativamente a quantidade de ho</t>
-  </si>
-  <si>
-    <t>Bruno da Silva</t>
-  </si>
-  <si>
-    <t>29848</t>
-  </si>
-  <si>
-    <t>Alteração da referência de Etiqueta para Romaneio - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Preparar Ambiente</t>
-  </si>
-  <si>
-    <t>36403</t>
-  </si>
-  <si>
-    <t>Informação desmoldagem incompleta - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Boa tarde, Informação do segundo tempo de desmoldagem não está aparecendo no email de desmoldagem conforme informação da OTF. Att.</t>
-  </si>
-  <si>
-    <t>Darlan Pressi</t>
-  </si>
-  <si>
-    <t>02/02/2026</t>
-  </si>
-  <si>
-    <t>36055</t>
-  </si>
-  <si>
-    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor criar um sistema de cadastro de identificador especial similar ao já existente da tela de cadastro TCPP45ID e consulta WCPP221J: Favor criar uma nova opção na tela TCPP45ID denominada "Possui controle ID especial?", sendo que se respondida como "SIM" permita o preenchimento dos seguin</t>
-  </si>
-  <si>
-    <t>14/01/2026</t>
-  </si>
-  <si>
-    <t>37394</t>
-  </si>
-  <si>
-    <t>Rateio Jato Dirigido 1 e 2 - Fazer QG para atualizar operações na apon3 com base no estado da peça (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde, Hoje (20/03/26 ) foi criado as operações jato dirigido para cadastrarmos os tempos na CPP para rateio de tempo Qlik. Precisamos que esse rateio seja retroativo. No apontamento eletrônico o estado da peça era somente apontado para informação e não apontado sua real operação. Precisamos que</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>36808</t>
-  </si>
-  <si>
-    <t>Melhorias setor 596</t>
-  </si>
-  <si>
-    <t>Bom dia, Gostaria de solicitar as seguintes melhorias no setor 596. 1 - Não deve ser possível movimentar o setor 596 caso tenha alguma pergunta ou item do formulário em aberto, conforme já é feito pra outros setores. 2 - Movimentação do 596 - para os fluxos 100, 102, 103 e 108 no momento da moviment</t>
-  </si>
-  <si>
-    <t>Paula Rosa M. Grando</t>
-  </si>
-  <si>
-    <t>Implementar Alerta de Solicitações de serviço com status de aguardando programação</t>
-  </si>
-  <si>
-    <t>Envio de ofertar trocar o usuário responsável</t>
-  </si>
-  <si>
-    <t>37160</t>
-  </si>
-  <si>
-    <t>Conversão da KB comercial para Gx18</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos migrar a aplicação do comercial, atualmente na versão gx75 para a versão 18. Principais entregas: - Levantar funcionalidades usadas e necessárias para a migração - Desenhar fluxo de trabalho com aplicação web - Converter objetos Atenciosamente,</t>
-  </si>
-  <si>
-    <t>36632</t>
-  </si>
-  <si>
-    <t>Multiplos de Caixa de ferro</t>
-  </si>
-  <si>
-    <t>Bom dia! Gostaria de criar um campo no ERP para cadastro de quantidade de peças por transferência (lote de transferência) Ex: Tipo de equipamento e Quantidade 1. Caixas de ferro: XX peças do modelo YYYYYY 2. Racks Stara: XX peças do modelo AAAAAA 3. Pallets: XX peças do modelo BBBBB Quem terá acesso</t>
-  </si>
-  <si>
-    <t>36206</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>22/01/2026</t>
-  </si>
-  <si>
-    <t>37412</t>
-  </si>
-  <si>
-    <t>Registro de Preset</t>
-  </si>
-  <si>
-    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
-  </si>
-  <si>
     <t>23/03/2026</t>
   </si>
   <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
     <t>37552</t>
   </si>
   <si>
@@ -975,9 +966,6 @@
     <t>Bloco K - Integração dados Altona / Benner.</t>
   </si>
   <si>
-    <t>Prezado, bom dia. Situação: Atualmente a integração dos dados Altona / Benner, para integrar o bloco K, precisa da intervenção de uma pessoa para disparar a rotina. Necessidade: Automatizar este processo. Ação: 1. Implementar status indicando que o dado está pronto para ser enviado para Benner. 2. A</t>
-  </si>
-  <si>
     <t>Aprimoramento Ailton - Frontend</t>
   </si>
   <si>
@@ -1068,12 +1056,6 @@
     <t>NOVA PERGUNTA ALERTA DE REVISÃO</t>
   </si>
   <si>
-    <t>Boa tarde, Favor incluir uma nova pergunta para todos os checklists de alerta de revisão. * A REVISÃO IMPACTA EM CUSTOS? Resposta "SIM" ou "NÃO". Caso a resposta seja "SIM" deve ser aberta uma segunda pergunta: * FOI SOLICITADA A REVISÃO DA FTF? Resposta "SIM" ou "NÃO". * A revisão só deve ser consi</t>
-  </si>
-  <si>
-    <t>30/01/2026</t>
-  </si>
-  <si>
     <t>37863</t>
   </si>
   <si>
@@ -1105,9 +1087,6 @@
   </si>
   <si>
     <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>22/04/2026</t>
   </si>
   <si>
     <t>38017</t>
@@ -1794,36 +1773,36 @@
         <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>19</v>
@@ -1841,7 +1820,7 @@
         <v>17</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>25</v>
@@ -1852,51 +1831,51 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
@@ -1908,7 +1887,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>17</v>
@@ -1917,13 +1896,13 @@
         <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>17</v>
@@ -1935,7 +1914,7 @@
         <v>21</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1952,7 +1931,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>29</v>
@@ -1970,33 +1949,33 @@
         <v>33</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>54</v>
@@ -2005,30 +1984,30 @@
         <v>19</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -2040,113 +2019,113 @@
         <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>24</v>
@@ -2155,71 +2134,71 @@
         <v>21</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>19</v>
@@ -2237,7 +2216,7 @@
         <v>17</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>25</v>
@@ -2260,7 +2239,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>29</v>
@@ -2278,16 +2257,16 @@
         <v>33</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -2304,10 +2283,10 @@
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>19</v>
@@ -2336,22 +2315,22 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>19</v>
@@ -2380,37 +2359,37 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>24</v>
@@ -2419,42 +2398,42 @@
         <v>25</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>24</v>
@@ -2463,39 +2442,39 @@
         <v>21</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>17</v>
@@ -2504,74 +2483,74 @@
         <v>20</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>30</v>
@@ -2589,7 +2568,7 @@
         <v>17</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>21</v>
@@ -2600,78 +2579,78 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>17</v>
@@ -2683,86 +2662,86 @@
         <v>21</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>24</v>
@@ -2771,27 +2750,27 @@
         <v>21</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>19</v>
@@ -2809,10 +2788,10 @@
         <v>17</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
@@ -2820,169 +2799,169 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>24</v>
@@ -2991,27 +2970,27 @@
         <v>21</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>30</v>
@@ -3029,10 +3008,10 @@
         <v>17</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>17</v>
@@ -3040,22 +3019,22 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>30</v>
@@ -3084,37 +3063,37 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>24</v>
@@ -3123,83 +3102,83 @@
         <v>21</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>17</v>
@@ -3208,15 +3187,15 @@
         <v>24</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -3228,7 +3207,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>17</v>
@@ -3237,13 +3216,13 @@
         <v>30</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>17</v>
@@ -3255,183 +3234,183 @@
         <v>21</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -3442,13 +3421,13 @@
         <v>15</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>29</v>
@@ -3466,95 +3445,95 @@
         <v>33</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>24</v>
@@ -3563,95 +3542,95 @@
         <v>21</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -3668,7 +3647,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>29</v>
@@ -3686,197 +3665,197 @@
         <v>33</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>17</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3888,7 +3867,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>17</v>
@@ -3897,69 +3876,69 @@
         <v>30</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -3976,7 +3955,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>29</v>
@@ -3994,16 +3973,16 @@
         <v>33</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -4020,7 +3999,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>29</v>
@@ -4038,48 +4017,48 @@
         <v>33</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>17</v>
@@ -4088,98 +4067,98 @@
         <v>20</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -4196,10 +4175,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -4228,125 +4207,125 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>241</v>
+        <v>17</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>24</v>
@@ -4355,100 +4334,100 @@
         <v>25</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4460,7 +4439,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>17</v>
@@ -4469,13 +4448,13 @@
         <v>30</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>17</v>
@@ -4487,71 +4466,71 @@
         <v>21</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>30</v>
@@ -4563,24 +4542,24 @@
         <v>32</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4592,22 +4571,22 @@
         <v>27</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>17</v>
@@ -4619,83 +4598,83 @@
         <v>21</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>55</v>
+        <v>261</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>17</v>
+        <v>263</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>17</v>
@@ -4704,186 +4683,186 @@
         <v>24</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -4894,13 +4873,13 @@
         <v>15</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>29</v>
@@ -4918,39 +4897,39 @@
         <v>33</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>17</v>
@@ -4965,7 +4944,7 @@
         <v>17</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>25</v>
@@ -4976,95 +4955,95 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -5076,54 +5055,54 @@
         <v>27</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>30</v>
@@ -5144,7 +5123,7 @@
         <v>24</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>17</v>
@@ -5152,66 +5131,66 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>19</v>
@@ -5229,10 +5208,10 @@
         <v>17</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>17</v>
@@ -5240,37 +5219,37 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>24</v>
@@ -5279,42 +5258,42 @@
         <v>25</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>24</v>
@@ -5323,139 +5302,139 @@
         <v>25</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
@@ -5472,10 +5451,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>19</v>
@@ -5496,7 +5475,7 @@
         <v>20</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>17</v>
@@ -5504,34 +5483,34 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>17</v>
@@ -5543,83 +5522,83 @@
         <v>21</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>17</v>
@@ -5628,42 +5607,42 @@
         <v>24</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>17</v>
@@ -5672,147 +5651,147 @@
         <v>24</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -5824,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>17</v>
@@ -5833,13 +5812,13 @@
         <v>30</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>17</v>
@@ -5851,174 +5830,174 @@
         <v>21</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>352</v>
+        <v>17</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>364</v>
+        <v>123</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>24</v>
@@ -6027,42 +6006,42 @@
         <v>21</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>364</v>
+        <v>123</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>24</v>
@@ -6071,7 +6050,7 @@
         <v>21</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -6088,7 +6067,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>29</v>
@@ -6106,60 +6085,60 @@
         <v>33</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -6175,23 +6154,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="D2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="E2" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6199,16 +6178,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6227,7 +6206,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6240,7 +6219,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23">
         <v>12</v>
@@ -6248,7 +6227,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6279,12 +6258,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B2">
         <v>102</v>
@@ -6308,25 +6287,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6337,19 +6316,19 @@
         <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6361,10 +6340,10 @@
         <v>53</v>
       </c>
       <c r="P10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q10">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -6381,27 +6360,27 @@
         <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="K11">
         <v>102</v>
       </c>
       <c r="M11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N11">
         <v>25</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q11">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -6422,24 +6401,24 @@
         <v>25</v>
       </c>
       <c r="Q12">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="N13">
         <v>4</v>
@@ -6448,38 +6427,38 @@
         <v>21</v>
       </c>
       <c r="Q13">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N14">
         <v>12</v>
       </c>
       <c r="P14" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -6487,7 +6466,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6495,7 +6474,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -6503,7 +6482,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -6514,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6522,35 +6501,35 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
@@ -6559,12 +6538,12 @@
         <v>458</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
@@ -6573,21 +6552,21 @@
         <v>458</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>26</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>28</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6598,10 +6577,10 @@
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6612,10 +6591,10 @@
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6626,10 +6605,10 @@
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>176</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6640,10 +6619,10 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6654,10 +6633,10 @@
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2026-12.xlsx
+++ b/utils/monday_sprint_sprint_2026-12.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="380">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>36046</t>
+    <t>11569521082</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,109 +87,124 @@
     <t>23/03/2026</t>
   </si>
   <si>
+    <t>19/04/2026</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>11793850875</t>
+  </si>
+  <si>
+    <t>ALTC  - Acompanhamento</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>29/04/2026</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Informar “baixa da produção”  e encerramento da OP</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>11793849096</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Registro de solda Digital - Chamar consulta de cargas e sequencias</t>
+  </si>
+  <si>
+    <t>28/04/2026</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>37766</t>
+  </si>
+  <si>
+    <t>Fundição</t>
+  </si>
+  <si>
+    <t>Campanha dos cadinhos</t>
+  </si>
+  <si>
+    <t>Criar sistemática de troca de campanha por forno sequencia somando a partir do cadinho anterior</t>
+  </si>
+  <si>
+    <t>Marcelo Americo</t>
+  </si>
+  <si>
+    <t>17/04/2026</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Consulta log de registros.</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>ALTC  - Acompanhamento</t>
-  </si>
-  <si>
-    <t>20/04/2026</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Informar “baixa da produção”  e encerramento da OP</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>37652</t>
-  </si>
-  <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Registro de solda Digital - Chamar consulta de cargas e sequencias</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>37766</t>
-  </si>
-  <si>
-    <t>Campanha dos cadinhos</t>
-  </si>
-  <si>
-    <t>Criar sistemática de troca de campanha por forno sequencia somando a partir do cadinho anterior</t>
-  </si>
-  <si>
-    <t>Marcelo Americo</t>
-  </si>
-  <si>
-    <t>17/04/2026</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Consulta log de registros.</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
     <t>Visualizar quantidades Produzidas no MES por atividade / maquina</t>
   </si>
   <si>
-    <t>36724</t>
+    <t>11793850718</t>
   </si>
   <si>
     <t>Alteração de registro de pintura</t>
@@ -198,883 +213,931 @@
     <t>A fazer</t>
   </si>
   <si>
-    <t>32079</t>
+    <t>11793850610</t>
+  </si>
+  <si>
+    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>37623</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Melhoria - Restrição de preenchimento</t>
+  </si>
+  <si>
+    <t>Boa tarde, Sandro, Gentileza criar a restrição no campo Data Entrega, que em caso do CFOP for inicial com 7, não permitir o preenchimento, ou apagar a informação. Está sendo incluso informações errôneas.</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>37461</t>
+  </si>
+  <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
+    <t>Altona || Adiantamento de Clientes do Exterior - Relatório de Variação Cambial - (Reunião) (copy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solicito a criação de uma rotina e posteriormente de um relatório que faça a demonstração da variação cambial dos adiantamentos de clientes do exterior. Para isso é preciso: 1) Criar um campo para cadastrar a moeda e sua respectiva cotação. Essa cotação será alimentada manualmente. Exemplo: Dólar – </t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
+  </si>
+  <si>
+    <t>37298</t>
+  </si>
+  <si>
+    <t>Melhoria | Custo de venda Orçamento Nacional (REUNIÃO)</t>
+  </si>
+  <si>
+    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
+  </si>
+  <si>
+    <t>11793845138</t>
+  </si>
+  <si>
+    <t>Layout ofertas exportação</t>
+  </si>
+  <si>
+    <t>03/05/2026</t>
+  </si>
+  <si>
+    <t>Visualizar todos os seus componentes (MRP) e quantidade consumida</t>
+  </si>
+  <si>
+    <t>11794986553</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Teste de nova Versão</t>
+  </si>
+  <si>
+    <t>11793864820</t>
+  </si>
+  <si>
+    <t>Coleta e identificação de sequencia - Analise de multiplas Fotos</t>
+  </si>
+  <si>
+    <t>37256</t>
+  </si>
+  <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
+    <t>Melhoria no sistema de ACR</t>
+  </si>
+  <si>
+    <t>Bom dia, Chamado para implementarmos melhorias no sistema de ACR. 1. Anexar análises de causa raiz junto aos pré formulários. 2. Identificar o tipo de gatilho no pré formulário 3. Melhorar resolução da tela de lista de causa raíz (está muito pequena) 4. Melhorar interface e interações para o usuário</t>
+  </si>
+  <si>
+    <t>Enzo Luiz Okabe Auad</t>
+  </si>
+  <si>
+    <t>12/05/2026</t>
+  </si>
+  <si>
+    <t>11793850719</t>
+  </si>
+  <si>
+    <t>Criar KB Genexus especifica para Registro de pinturas</t>
+  </si>
+  <si>
+    <t>36541</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
+  </si>
+  <si>
+    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
+  </si>
+  <si>
+    <t>Alini Ferreira Ganda</t>
+  </si>
+  <si>
+    <t>11782364629</t>
+  </si>
+  <si>
+    <t>Gráfico de barras empilhadas “reprovação ao longo dos meses”</t>
+  </si>
+  <si>
+    <t>02/05/2026</t>
+  </si>
+  <si>
+    <t>11584908721</t>
+  </si>
+  <si>
+    <t>Tela de Matrículas / Participantes</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>11793849094</t>
+  </si>
+  <si>
+    <t>CRIAÇÃO DE B.I. PARA ACOMPANHAMENTO DE RESULTADOS DE ENSAIOS MECÂNICO</t>
+  </si>
+  <si>
+    <t>36219</t>
+  </si>
+  <si>
+    <t>Controladoria</t>
+  </si>
+  <si>
+    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
+  </si>
+  <si>
+    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>23/04/2026</t>
+  </si>
+  <si>
+    <t>37751</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Melhoria no modulo de estorno para item de estoque</t>
+  </si>
+  <si>
+    <t>Boa tarde! Atualmente, o processo de estorno de itens de estoque é trabalhoso, pois exige várias etapas para sua execução. Diante disso, solicitamos a disponibilização, dentro do WMS do Almoxarifado, de um processo unificado de estorno, no qual o colaborador possa: Informar o código do item a ser es</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>37526</t>
   </si>
   <si>
     <t>TI</t>
   </si>
   <si>
-    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
+    <t>PDI - Relatório de apontamentos</t>
+  </si>
+  <si>
+    <t>Verificar a situação apresentada pelo usuário Gerson Mendonça: Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Alexandre Longo</t>
+  </si>
+  <si>
+    <t>5813984939</t>
+  </si>
+  <si>
+    <t>Sistema de Separação Part 1/2</t>
+  </si>
+  <si>
+    <t>08/01/2024</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>37575</t>
+  </si>
+  <si>
+    <t>ADICIONAR NO APONTAMENTO DIGITAL - 279 - RETRABALHO DE ESMERIL APÓS VISUAL.</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito adicionar a opção no apontamento digital, conforme sugestão abaixo; Operação - Descrição da Operação. 279 - RETRABALHO DE ESMERIL APÓS VISUAL. MOTIVO: Os ajustadores precisam RETRABALHAR algumas áreas que o inspetor da qualidade julga não conforme. At.te,</t>
+  </si>
+  <si>
+    <t>Juliano Carriel</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>37746</t>
+  </si>
+  <si>
+    <t>Altona || Consignados - Diferença nos saldos</t>
+  </si>
+  <si>
+    <t>Sandro! O estoque de consignados ainda não fecha, perceba na comparação que eu fiz. Nela eu conferi entradas e consumo no Benner e no SNB, mas os saldos finais são diferentes. De onde eu tirei o saldo de R$ 521.678,11. Usando teu relatório e excluindo alguns grupos que não devem estar ali: Podes ver</t>
+  </si>
+  <si>
+    <t>37129</t>
+  </si>
+  <si>
+    <t>Em ambos os alertas das implementações 1 e 2 devem ser gerados relatórios mensais para cada implementação,</t>
+  </si>
+  <si>
+    <t>Bom dia, Chamado Prioritário para correção de não conformidade identificada durante auditoria terceirizada não oficial da ISO 9001. Recentemente foi feita uma alteração no sistema na qual as ordens preventivas ao checar na caixa ilustrada abaixo sejam abertas como uma SS (solicitação de serviço) com</t>
+  </si>
+  <si>
+    <t>37466</t>
+  </si>
+  <si>
+    <t>Calibração de Maquinas de Solda</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos de uma alteração no sistema de manutenção, com relação a baixa de OS para maquinas de solda (família 9). Precisamos que seja feito uma automação, para quando o mantenedor selecione o defeito do equipamento no momento do apontamento, alguns defeitos permitam que a OS seja encerrad</t>
+  </si>
+  <si>
+    <t>Luiz Henrique Rocha Junior</t>
+  </si>
+  <si>
+    <t>11134485879</t>
+  </si>
+  <si>
+    <t>Liberação Ensaio Mecanico Automatico</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>11793845016</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
+  </si>
+  <si>
+    <t>37499</t>
+  </si>
+  <si>
+    <t>Alteração sistema registro USE-ULE Windows</t>
+  </si>
+  <si>
+    <t>Bom dia, Necessitamos que seja feita uma alteração no sistema de registro USE-ULE, precisamos que as imagens que ficam anexas as perguntas, quando exibidas pelo relatório do botão "Imprime Registro" sejam de um tamanho maior, que seja possível analisar de forma clara pelo computador. Sugerimos que s</t>
+  </si>
+  <si>
+    <t>João Eduardo Zarth</t>
+  </si>
+  <si>
+    <t>11793867572</t>
+  </si>
+  <si>
+    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada</t>
+  </si>
+  <si>
+    <t>Tela apoio para forçar envio de dados.</t>
+  </si>
+  <si>
+    <t>37230</t>
+  </si>
+  <si>
+    <t>Melhoria SMI - Solicitação da supervisão - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>11793864814</t>
+  </si>
+  <si>
+    <t>Sequencial number Clientes</t>
+  </si>
+  <si>
+    <t>37300</t>
+  </si>
+  <si>
+    <t>Engenharia</t>
+  </si>
+  <si>
+    <t>AVISO DE SETORES COM CHECKLIST E/OU FORMULÁRIO EM ABERTO E SALDO JÁ MOVIMENTADO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor criar um aviso semanal por e-mail dos setores que possuem checklists e/ou formulários em aberto (Não) e que estejam com a quantidade despachada igual a quantidade programada. Esse aviso deve ser via outlook para o e-mail arquivo@altona.com.br, no PDF anexo deve conter sequência e quai</t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy) (copy) (copy)</t>
+  </si>
+  <si>
+    <t>11793865603</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Erro Planilhão - Itens conjuntos</t>
+  </si>
+  <si>
+    <t>37446</t>
+  </si>
+  <si>
+    <t>PAINEL DE VISUALIZAÇÃO PARA LINHAS UPR</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicitamos a elaboração de um painel de visualização para as linhas UPR, estruturado nos mesmos padrões utilizados para os painéis de jato e manipuladores, com o objetivo de aprimorar o acompanhamento por parte da liderança. A disposição;</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>32150</t>
+  </si>
+  <si>
+    <t>Inventario WMS - Registro de Ajuste de Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>37169</t>
+  </si>
+  <si>
+    <t>Alteração em relatorio dentro do sistema "Apontamento de produção"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, solicito a alteração no relatório de apontamento por funcionário quando "gerar o Excel". Preciso que no relatório saia o turno e o setor que cada funcionário faz parte ( inspeção END ou DIM). Motivo: Facilitar e otimizar o tempo de elaboração do relatório disponibilizado para liderança e </t>
+  </si>
+  <si>
+    <t>Gerson Mendonça</t>
+  </si>
+  <si>
+    <t>Consulta geral de OPs - Dataviews</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>37095</t>
+  </si>
+  <si>
+    <t>Logistica</t>
+  </si>
+  <si>
+    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
+  </si>
+  <si>
+    <t>Rodrigo Santos Rocha</t>
+  </si>
+  <si>
+    <t>36232</t>
+  </si>
+  <si>
+    <t>Mecânica</t>
+  </si>
+  <si>
+    <t>Report técnico - Acompanhamento - Homologação</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>Atualizar campos: data, hora e prazo da proposta</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>25310</t>
+  </si>
+  <si>
+    <t>Sistema de Controle de Orçamento de Entregas de Venda</t>
+  </si>
+  <si>
+    <t>Boa Tarde Segue anexo escopo para criação do sistema de controle de orçamentos de Entrega de venda, para comparação com o realizado e provisionamento de custo para a controladoria.</t>
+  </si>
+  <si>
+    <t>Visualização completa dos Dados da OP</t>
+  </si>
+  <si>
+    <t>Consulta geral de OPs (filtro por datas, modelo, sequencia, situação)</t>
+  </si>
+  <si>
+    <t>37781</t>
+  </si>
+  <si>
+    <t>Controle de sequência por nota fiscal - Alerta notas fiscais sem sequencia informada</t>
+  </si>
+  <si>
+    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
   </si>
   <si>
     <t>Edson João Hammermeister</t>
   </si>
   <si>
-    <t>37623</t>
-  </si>
-  <si>
-    <t>Melhoria - Restrição de preenchimento</t>
-  </si>
-  <si>
-    <t>Boa tarde, Sandro, Gentileza criar a restrição no campo Data Entrega, que em caso do CFOP for inicial com 7, não permitir o preenchimento, ou apagar a informação. Está sendo incluso informações errôneas.</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>07/05/2026</t>
-  </si>
-  <si>
-    <t>37461</t>
-  </si>
-  <si>
-    <t>Altona || Adiantamento de Clientes do Exterior - Relatório de Variação Cambial - (Reunião) (copy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solicito a criação de uma rotina e posteriormente de um relatório que faça a demonstração da variação cambial dos adiantamentos de clientes do exterior. Para isso é preciso: 1) Criar um campo para cadastrar a moeda e sua respectiva cotação. Essa cotação será alimentada manualmente. Exemplo: Dólar – </t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>37298</t>
-  </si>
-  <si>
-    <t>Melhoria | Custo de venda Orçamento Nacional (REUNIÃO)</t>
-  </si>
-  <si>
-    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
-  </si>
-  <si>
-    <t>37530</t>
-  </si>
-  <si>
-    <t>Layout ofertas exportação</t>
-  </si>
-  <si>
-    <t>Visualizar todos os seus componentes (MRP) e quantidade consumida</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Teste de nova Versão</t>
-  </si>
-  <si>
-    <t>35602</t>
-  </si>
-  <si>
-    <t>Coleta e identificação de sequencia - Analise de multiplas Fotos</t>
-  </si>
-  <si>
-    <t>37256</t>
-  </si>
-  <si>
-    <t>Melhoria no sistema de ACR</t>
-  </si>
-  <si>
-    <t>Bom dia, Chamado para implementarmos melhorias no sistema de ACR. 1. Anexar análises de causa raiz junto aos pré formulários. 2. Identificar o tipo de gatilho no pré formulário 3. Melhorar resolução da tela de lista de causa raíz (está muito pequena) 4. Melhorar interface e interações para o usuário</t>
-  </si>
-  <si>
-    <t>Enzo Luiz Okabe Auad</t>
-  </si>
-  <si>
-    <t>12/05/2026</t>
-  </si>
-  <si>
-    <t>19909</t>
-  </si>
-  <si>
-    <t>Criar KB Genexus especifica para Registro de pinturas</t>
-  </si>
-  <si>
-    <t>36541</t>
-  </si>
-  <si>
-    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
-  </si>
-  <si>
-    <t>36816</t>
-  </si>
-  <si>
-    <t>Gráfico de barras empilhadas “reprovação ao longo dos meses”</t>
-  </si>
-  <si>
-    <t>35764</t>
-  </si>
-  <si>
-    <t>Tela de Matrículas / Participantes</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>CRIAÇÃO DE B.I. PARA ACOMPANHAMENTO DE RESULTADOS DE ENSAIOS MECÂNICO</t>
-  </si>
-  <si>
-    <t>36219</t>
-  </si>
-  <si>
-    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
-  </si>
-  <si>
-    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>37751</t>
-  </si>
-  <si>
-    <t>Almoxarifado</t>
-  </si>
-  <si>
-    <t>Melhoria no modulo de estorno para item de estoque</t>
-  </si>
-  <si>
-    <t>Boa tarde! Atualmente, o processo de estorno de itens de estoque é trabalhoso, pois exige várias etapas para sua execução. Diante disso, solicitamos a disponibilização, dentro do WMS do Almoxarifado, de um processo unificado de estorno, no qual o colaborador possa: Informar o código do item a ser es</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>37526</t>
-  </si>
-  <si>
-    <t>PDI - Relatório de apontamentos</t>
-  </si>
-  <si>
-    <t>Verificar a situação apresentada pelo usuário Gerson Mendonça: Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Alexandre Longo</t>
-  </si>
-  <si>
-    <t>22/04/2026</t>
+    <t>36624</t>
+  </si>
+  <si>
+    <t>Problema</t>
+  </si>
+  <si>
+    <t>Indicadores de retrabalho</t>
+  </si>
+  <si>
+    <t>Bom dia. Foi percebido diferen?as entre gr?ficos e dados nos indicadores abaixo. Favor verificar. No exemplo, foi filtrado os setores da KOMATSU. Selecionado o top 3 modelos com maior n?mero de horas em retrabalho. Ao extrair o excel, o total de horas ultrapassa significativamente a quantidade de ho</t>
+  </si>
+  <si>
+    <t>Bruno da Silva</t>
+  </si>
+  <si>
+    <t>29848</t>
+  </si>
+  <si>
+    <t>Alteração da referência de Etiqueta para Romaneio - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
+  </si>
+  <si>
+    <t>11793870394</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Preparar Ambiente</t>
+  </si>
+  <si>
+    <t>36403</t>
+  </si>
+  <si>
+    <t>Informação desmoldagem incompleta - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Boa tarde, Informação do segundo tempo de desmoldagem não está aparecendo no email de desmoldagem conforme informação da OTF. Att.</t>
+  </si>
+  <si>
+    <t>Darlan Pressi</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>11793884069</t>
+  </si>
+  <si>
+    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER</t>
+  </si>
+  <si>
+    <t>37394</t>
+  </si>
+  <si>
+    <t>Rateio Jato Dirigido 1 e 2 - Fazer QG para atualizar operações na apon3 com base no estado da peça (copy)</t>
+  </si>
+  <si>
+    <t>Boa tarde, Hoje (20/03/26 ) foi criado as operações jato dirigido para cadastrarmos os tempos na CPP para rateio de tempo Qlik. Precisamos que esse rateio seja retroativo. No apontamento eletrônico o estado da peça era somente apontado para informação e não apontado sua real operação. Precisamos que</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>11448210572</t>
+  </si>
+  <si>
+    <t>Melhorias setor 596</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>Implementar Alerta de Solicitações de serviço com status de aguardando programação</t>
+  </si>
+  <si>
+    <t>Envio de ofertar trocar o usuário responsável</t>
+  </si>
+  <si>
+    <t>37160</t>
+  </si>
+  <si>
+    <t>Conversão da KB comercial para Gx18</t>
+  </si>
+  <si>
+    <t>Prezados, Precisamos migrar a aplicação do comercial, atualmente na versão gx75 para a versão 18. Principais entregas: - Levantar funcionalidades usadas e necessárias para a migração - Desenhar fluxo de trabalho com aplicação web - Converter objetos Atenciosamente,</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>11793867919</t>
+  </si>
+  <si>
+    <t>Multiplos de Caixa de ferro</t>
+  </si>
+  <si>
+    <t>36206</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>37412</t>
+  </si>
+  <si>
+    <t>Usinagem</t>
+  </si>
+  <si>
+    <t>Registro de Preset</t>
+  </si>
+  <si>
+    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
+  </si>
+  <si>
+    <t>Lucas Sebold Movidesk</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>37552</t>
+  </si>
+  <si>
+    <t>Requisições BINAAR</t>
+  </si>
+  <si>
+    <t>Bom dia. Solicitação de implementação de sistema WMS para requisição de itens na manutenção de equipamentos pneumáticos. Utilização de coletor para leitura dos itens utilizados em cada equipamentos consertado. Importante ressaltar que existem itens utilizados que não são fornecidos pela BINAAR, como</t>
+  </si>
+  <si>
+    <t>26/04/2026</t>
+  </si>
+  <si>
+    <t>37753</t>
+  </si>
+  <si>
+    <t>Integração da maquina - Analise</t>
+  </si>
+  <si>
+    <t>Boa tarde, @Edson João Hammermeister conforme conversamos na reunião, favor seguir com a integração da máquina Cenci, acredito que já esteva conversando com eles. https://documenter.getpostman.com/view/24484248/2sA3kRJPEZ#282fad9d-f4d0-48ff-b7c0-62f4e8fe2ba5 Fico no aguardo do retorno. Att</t>
+  </si>
+  <si>
+    <t>Alan Jonis da Silva</t>
+  </si>
+  <si>
+    <t>Em Análise</t>
+  </si>
+  <si>
+    <t>30069</t>
+  </si>
+  <si>
+    <t>Controle de Importação - integração financeira</t>
+  </si>
+  <si>
+    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
+  </si>
+  <si>
+    <t>Esses relatórios também devem estar disponíveis na aba de relatórios para extração em excel a qualquer momento</t>
+  </si>
+  <si>
+    <t>37749</t>
+  </si>
+  <si>
+    <t>Estorno para itens de saldo fornecedor</t>
+  </si>
+  <si>
+    <t>Boa tarde! Atualmente temos disponível a modalidade saldo fornecedor para os fornecedores Fiedler e Binaar. No entanto, o sistema não disponibiliza a opção de estorno em casos de requisições realizadas de forma indevida. Diante disso, solicitamos a inclusão de uma funcionalidade de estorno para aten</t>
+  </si>
+  <si>
+    <t>Como teremos 3 modelagens as op’s poderão ter quantidades diferentes nas modelagens, validar com o pessoal do APS essa interligação. (copy)</t>
+  </si>
+  <si>
+    <t>11793883786</t>
+  </si>
+  <si>
+    <t>Solicitação de melhoria no WMS – Pré-lista (EPI)</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>37791</t>
+  </si>
+  <si>
+    <t>Solicitação de Análise - Sistema de Custeio</t>
+  </si>
+  <si>
+    <t>Alexandre, bom dia! Gentileza verificar, no cálculo do custeio de fevereiro 2026, a seq. 376MI estava com informação errada de 24 pçs, enquanto que é sequência única.</t>
+  </si>
+  <si>
+    <t>37563</t>
+  </si>
+  <si>
+    <t>Corridas Fora de Liga</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos que esse relatório gere a opção de excel. Com as informações de Forno, Corrida, Liga, Faixa Mínima, Faixa Máxima e mensurado Local onde pode ser adicionado o botão, após colocar as informações de ano e forno abre essa tela, e nessa tela incluir um botão para gerar um excel de t</t>
+  </si>
+  <si>
+    <t>Espectrometria</t>
+  </si>
+  <si>
+    <t>37200</t>
+  </si>
+  <si>
+    <t>Apontamento Escarfa - Apresentacao e acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos da elaboração de um sistema web para o corte escarfa UPR. São duas linhas apontadas por um operador simultaneamente (linha 1 e linha 2), Pra facilitar visual do operador e dinâmica dividir as duas linhas na mesma tela, mas com todos os resultados separados. As sequencias devem se</t>
+  </si>
+  <si>
+    <t>11678210415</t>
+  </si>
+  <si>
+    <t>Criar API para receber informações do MES para a abertura da SS</t>
+  </si>
+  <si>
+    <t>21/04/2026</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>11678210658</t>
+  </si>
+  <si>
+    <t>Tela de Cadastro de Turmas</t>
+  </si>
+  <si>
+    <t>37330</t>
+  </si>
+  <si>
+    <t>MELHORIAS NO APONTAEMNTO LINHA FASE 4 - UPR</t>
+  </si>
+  <si>
+    <t>Boa tarde, Estamos enfrentando uma dificuldade em dividir tempos na linha fase 4 que se encontra hoje em teste. Precisamos que o tempo da peça (sequência) que se encontra finalizada (100% indicado pelo operador) com retoques marcadas pela inspeção próximo a troca de turno, seja somado ao apontamento</t>
+  </si>
+  <si>
+    <t>33631</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - Custos</t>
+  </si>
+  <si>
+    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
+  </si>
+  <si>
+    <t>Automatização DRE Gerencial - Pós fechamento de custos</t>
+  </si>
+  <si>
+    <t>36722</t>
+  </si>
+  <si>
+    <t>Bloco K - Integração dados Altona / Benner.</t>
+  </si>
+  <si>
+    <t>Prezado, bom dia. Situação: Atualmente a integração dos dados Altona / Benner, para integrar o bloco K, precisa da intervenção de uma pessoa para disparar a rotina. Necessidade: Automatizar este processo. Ação: 1. Implementar status indicando que o dado está pronto para ser enviado para Benner. 2. A</t>
+  </si>
+  <si>
+    <t>11679604593</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Frontend</t>
+  </si>
+  <si>
+    <t>36915</t>
+  </si>
+  <si>
+    <t>SOBREPOSIÇÃO DE ALERTAS</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor verificar a sistemática de alerta de revisão no sistema PCP, pois está havendo sobreposições de comandos no aviso do alerta de revisão: At.te</t>
+  </si>
+  <si>
+    <t>37361</t>
+  </si>
+  <si>
+    <t>Base Histórica da Data de Reconhecimento  de Receita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
+  </si>
+  <si>
+    <t>37190</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
+  </si>
+  <si>
+    <t>Guilherme Ferreira</t>
+  </si>
+  <si>
+    <t>32141</t>
+  </si>
+  <si>
+    <t>Cadastro de Embalagem no CPP (APS)</t>
+  </si>
+  <si>
+    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>Implementar Alerta Ordens de serviços com data de programação (já programadas) e não foram executadas</t>
+  </si>
+  <si>
+    <t>37745</t>
+  </si>
+  <si>
+    <t>Sistema de Apontamento corte pó de ferro</t>
+  </si>
+  <si>
+    <t>Bom dia preciso que seja feito algumas alterações e seja adicionado algumas novas funções no sistema de apontamentos dos tablets no pó de ferro. · Adicionar modelo ao lado da sequência. Durante o apontamento e após finalizado é necessário adicionar o modelo correspondente a sequência para o conhecim</t>
+  </si>
+  <si>
+    <t>Amanda Vitoria Aroeira Marinho</t>
+  </si>
+  <si>
+    <t>32133</t>
+  </si>
+  <si>
+    <t>Novo Recurso</t>
+  </si>
+  <si>
+    <t>Automatização planilha comercial - PARTE 2/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
+  </si>
+  <si>
+    <t>Jacson Schneider Movidesk</t>
+  </si>
+  <si>
+    <t>Revisar os campos: data, hora e prazo da proposta</t>
+  </si>
+  <si>
+    <t>36376</t>
+  </si>
+  <si>
+    <t>NOVA PERGUNTA ALERTA DE REVISÃO</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor incluir uma nova pergunta para todos os checklists de alerta de revisão. * A REVISÃO IMPACTA EM CUSTOS? Resposta "SIM" ou "NÃO". Caso a resposta seja "SIM" deve ser aberta uma segunda pergunta: * FOI SOLICITADA A REVISÃO DA FTF? Resposta "SIM" ou "NÃO". * A revisão só deve ser consi</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>37863</t>
+  </si>
+  <si>
+    <t>Alteração manual de campanhas</t>
+  </si>
+  <si>
+    <t>Solicito possibilidade de alteração manual nesta tela</t>
+  </si>
+  <si>
+    <t>37774</t>
+  </si>
+  <si>
+    <t>(Oferta/oportunidade - identificação analista de vendas.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezado, bom dia. O processo que migra as ofertas/oportunidades para o CRM está definindo o ADMINISTRADOR como responsável por todas elas. Isso gera um problema quando o usuário tenta localizar suas próprias ofertas/oportunidades no CRM. A Senior analisou a situação e sugeriu uma forma de contornar </t>
+  </si>
+  <si>
+    <t>38015</t>
+  </si>
+  <si>
+    <t>Inclusão de parâmetro de exportação de notas</t>
+  </si>
+  <si>
+    <t>Bom dia! Peço que na hora de exportar as notas para o sistema do Benner, seja adicionado mais um parâmetro para os produtos, conforme demonstrado abaixo: Esse ajuste já foi feito na tabela [ED_DOCUMENTOITENS], mas precisa ser feito também na [FN_DOCUMENTOLANCOBSAJUSTES].</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>38017</t>
+  </si>
+  <si>
+    <t>Função de Anexo - Recolocar botão para enviar anexo para a calibragem</t>
+  </si>
+  <si>
+    <t>Boa tarde, Chamado já executado, somente abrindo a solicitação para mapeamento da área. Tiago havia executado uma alteração no botão de anexos do equipamento na pagina de baixa de ordens de serviço, e depois descobri que precisávamos manter o antigo botão em funcionamento pois eram documentos enviad</t>
+  </si>
+  <si>
+    <t>Criar estrutura para controlar mais de 01 modelo por placa</t>
+  </si>
+  <si>
+    <t>Consulta para SS e OS em atraso</t>
+  </si>
+  <si>
+    <t>Dashboard de Change Log - Governança de TI</t>
+  </si>
+  <si>
+    <t>Período</t>
+  </si>
+  <si>
+    <t>Jan/2024</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Tickets corporativos para intranet / Power BI / Excel</t>
+  </si>
+  <si>
+    <t>Total de tickets</t>
+  </si>
+  <si>
+    <t>% dentro do SLA</t>
+  </si>
+  <si>
+    <t>Tempo médio (dias)</t>
+  </si>
+  <si>
+    <t>Áreas atendidas</t>
+  </si>
+  <si>
+    <t>Status final</t>
+  </si>
+  <si>
+    <t>Encerrado</t>
+  </si>
+  <si>
+    <t>Resumo Executivo</t>
+  </si>
+  <si>
+    <t>Tickets por Área</t>
+  </si>
+  <si>
+    <t>Distribuição por Tipo</t>
+  </si>
+  <si>
+    <t>Cumprimento SLA (15 dias)</t>
+  </si>
+  <si>
+    <t>Status Final</t>
+  </si>
+  <si>
+    <t>Tickets por Semana</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Muito Alta</t>
   </si>
   <si>
     <t>Sim</t>
-  </si>
-  <si>
-    <t>23839</t>
-  </si>
-  <si>
-    <t>Sistema de Separação Part 1/2</t>
-  </si>
-  <si>
-    <t>08/01/2024</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>37575</t>
-  </si>
-  <si>
-    <t>Fundição</t>
-  </si>
-  <si>
-    <t>ADICIONAR NO APONTAMENTO DIGITAL - 279 - RETRABALHO DE ESMERIL APÓS VISUAL.</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito adicionar a opção no apontamento digital, conforme sugestão abaixo; Operação - Descrição da Operação. 279 - RETRABALHO DE ESMERIL APÓS VISUAL. MOTIVO: Os ajustadores precisam RETRABALHAR algumas áreas que o inspetor da qualidade julga não conforme. At.te,</t>
-  </si>
-  <si>
-    <t>Juliano Carriel</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>37746</t>
-  </si>
-  <si>
-    <t>Altona || Consignados - Diferença nos saldos</t>
-  </si>
-  <si>
-    <t>Sandro! O estoque de consignados ainda não fecha, perceba na comparação que eu fiz. Nela eu conferi entradas e consumo no Benner e no SNB, mas os saldos finais são diferentes. De onde eu tirei o saldo de R$ 521.678,11. Usando teu relatório e excluindo alguns grupos que não devem estar ali: Podes ver</t>
-  </si>
-  <si>
-    <t>37129</t>
-  </si>
-  <si>
-    <t>Em ambos os alertas das implementações 1 e 2 devem ser gerados relatórios mensais para cada implementação,</t>
-  </si>
-  <si>
-    <t>Bom dia, Chamado Prioritário para correção de não conformidade identificada durante auditoria terceirizada não oficial da ISO 9001. Recentemente foi feita uma alteração no sistema na qual as ordens preventivas ao checar na caixa ilustrada abaixo sejam abertas como uma SS (solicitação de serviço) com</t>
-  </si>
-  <si>
-    <t>37466</t>
-  </si>
-  <si>
-    <t>Manutenção</t>
-  </si>
-  <si>
-    <t>Calibração de Maquinas de Solda</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos de uma alteração no sistema de manutenção, com relação a baixa de OS para maquinas de solda (família 9). Precisamos que seja feito uma automação, para quando o mantenedor selecione o defeito do equipamento no momento do apontamento, alguns defeitos permitam que a OS seja encerrad</t>
-  </si>
-  <si>
-    <t>Luiz Henrique Rocha Junior</t>
-  </si>
-  <si>
-    <t>36063</t>
-  </si>
-  <si>
-    <t>Liberação Ensaio Mecanico Automatico</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>23838</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
-  </si>
-  <si>
-    <t>37499</t>
-  </si>
-  <si>
-    <t>Alteração sistema registro USE-ULE Windows</t>
-  </si>
-  <si>
-    <t>Bom dia, Necessitamos que seja feita uma alteração no sistema de registro USE-ULE, precisamos que as imagens que ficam anexas as perguntas, quando exibidas pelo relatório do botão "Imprime Registro" sejam de um tamanho maior, que seja possível analisar de forma clara pelo computador. Sugerimos que s</t>
-  </si>
-  <si>
-    <t>João Eduardo Zarth</t>
-  </si>
-  <si>
-    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada</t>
-  </si>
-  <si>
-    <t>Tela apoio para forçar envio de dados.</t>
-  </si>
-  <si>
-    <t>37230</t>
-  </si>
-  <si>
-    <t>Melhoria SMI - Solicitação da supervisão - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>36641</t>
-  </si>
-  <si>
-    <t>Sequencial number Clientes</t>
-  </si>
-  <si>
-    <t>37300</t>
-  </si>
-  <si>
-    <t>Engenharia</t>
-  </si>
-  <si>
-    <t>AVISO DE SETORES COM CHECKLIST E/OU FORMULÁRIO EM ABERTO E SALDO JÁ MOVIMENTADO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor criar um aviso semanal por e-mail dos setores que possuem checklists e/ou formulários em aberto (Não) e que estejam com a quantidade despachada igual a quantidade programada. Esse aviso deve ser via outlook para o e-mail arquivo@altona.com.br, no PDF anexo deve conter sequência e quai</t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy) (copy) (copy)</t>
-  </si>
-  <si>
-    <t>35727</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Erro Planilhão - Itens conjuntos</t>
-  </si>
-  <si>
-    <t>Boa tarde Pela primeira vez na UPR, teremos um item de fundido que atenderá a dois conjuntos diferentes. Atualmente, temos 13 peças do fundido em processo e 4 peças dos conjuntos em depósito. No entanto, o Planilhão está considerando apenas 1 peça em estoque, não reconhecendo as outras 3. É importan</t>
-  </si>
-  <si>
-    <t>Taynara Frare</t>
-  </si>
-  <si>
-    <t>37446</t>
-  </si>
-  <si>
-    <t>PAINEL DE VISUALIZAÇÃO PARA LINHAS UPR</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicitamos a elaboração de um painel de visualização para as linhas UPR, estruturado nos mesmos padrões utilizados para os painéis de jato e manipuladores, com o objetivo de aprimorar o acompanhamento por parte da liderança. A disposição;</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>32150</t>
-  </si>
-  <si>
-    <t>Inventario WMS - Registro de Ajuste de Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>37169</t>
-  </si>
-  <si>
-    <t>Alteração em relatorio dentro do sistema "Apontamento de produção"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, solicito a alteração no relatório de apontamento por funcionário quando "gerar o Excel". Preciso que no relatório saia o turno e o setor que cada funcionário faz parte ( inspeção END ou DIM). Motivo: Facilitar e otimizar o tempo de elaboração do relatório disponibilizado para liderança e </t>
-  </si>
-  <si>
-    <t>Gerson Mendonça</t>
-  </si>
-  <si>
-    <t>Consulta geral de OPs - Dataviews</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>37095</t>
-  </si>
-  <si>
-    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
-  </si>
-  <si>
-    <t>Rodrigo Santos Rocha</t>
-  </si>
-  <si>
-    <t>36232</t>
-  </si>
-  <si>
-    <t>Report técnico - Acompanhamento - Homologação</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
-  </si>
-  <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
-    <t>Atualizar campos: data, hora e prazo da proposta</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>25310</t>
-  </si>
-  <si>
-    <t>Sistema de Controle de Orçamento de Entregas de Venda</t>
-  </si>
-  <si>
-    <t>Boa Tarde Segue anexo escopo para criação do sistema de controle de orçamentos de Entrega de venda, para comparação com o realizado e provisionamento de custo para a controladoria.</t>
-  </si>
-  <si>
-    <t>Visualização completa dos Dados da OP</t>
-  </si>
-  <si>
-    <t>Consulta geral de OPs (filtro por datas, modelo, sequencia, situação)</t>
-  </si>
-  <si>
-    <t>37781</t>
-  </si>
-  <si>
-    <t>Controle de sequência por nota fiscal - Alerta notas fiscais sem sequencia informada</t>
-  </si>
-  <si>
-    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
-  </si>
-  <si>
-    <t>36624</t>
-  </si>
-  <si>
-    <t>Problema</t>
-  </si>
-  <si>
-    <t>Indicadores de retrabalho</t>
-  </si>
-  <si>
-    <t>Bom dia. Foi percebido diferen?as entre gr?ficos e dados nos indicadores abaixo. Favor verificar. No exemplo, foi filtrado os setores da KOMATSU. Selecionado o top 3 modelos com maior n?mero de horas em retrabalho. Ao extrair o excel, o total de horas ultrapassa significativamente a quantidade de ho</t>
-  </si>
-  <si>
-    <t>Bruno da Silva</t>
-  </si>
-  <si>
-    <t>29848</t>
-  </si>
-  <si>
-    <t>Alteração da referência de Etiqueta para Romaneio - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Preparar Ambiente</t>
-  </si>
-  <si>
-    <t>36403</t>
-  </si>
-  <si>
-    <t>Informação desmoldagem incompleta - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Boa tarde, Informação do segundo tempo de desmoldagem não está aparecendo no email de desmoldagem conforme informação da OTF. Att.</t>
-  </si>
-  <si>
-    <t>Darlan Pressi</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>36055</t>
-  </si>
-  <si>
-    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER</t>
-  </si>
-  <si>
-    <t>37394</t>
-  </si>
-  <si>
-    <t>Rateio Jato Dirigido 1 e 2 - Fazer QG para atualizar operações na apon3 com base no estado da peça (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde, Hoje (20/03/26 ) foi criado as operações jato dirigido para cadastrarmos os tempos na CPP para rateio de tempo Qlik. Precisamos que esse rateio seja retroativo. No apontamento eletrônico o estado da peça era somente apontado para informação e não apontado sua real operação. Precisamos que</t>
-  </si>
-  <si>
-    <t>20/05/2026</t>
-  </si>
-  <si>
-    <t>36808</t>
-  </si>
-  <si>
-    <t>Melhorias setor 596</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>Implementar Alerta de Solicitações de serviço com status de aguardando programação</t>
-  </si>
-  <si>
-    <t>Envio de ofertar trocar o usuário responsável</t>
-  </si>
-  <si>
-    <t>37160</t>
-  </si>
-  <si>
-    <t>Conversão da KB comercial para Gx18</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos migrar a aplicação do comercial, atualmente na versão gx75 para a versão 18. Principais entregas: - Levantar funcionalidades usadas e necessárias para a migração - Desenhar fluxo de trabalho com aplicação web - Converter objetos Atenciosamente,</t>
-  </si>
-  <si>
-    <t>06/04/2026</t>
-  </si>
-  <si>
-    <t>36632</t>
-  </si>
-  <si>
-    <t>Multiplos de Caixa de ferro</t>
-  </si>
-  <si>
-    <t>36206</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>37412</t>
-  </si>
-  <si>
-    <t>Registro de Preset</t>
-  </si>
-  <si>
-    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
-  </si>
-  <si>
-    <t>Lucas Sebold Movidesk</t>
-  </si>
-  <si>
-    <t>18/05/2026</t>
-  </si>
-  <si>
-    <t>37552</t>
-  </si>
-  <si>
-    <t>Requisições BINAAR</t>
-  </si>
-  <si>
-    <t>Bom dia. Solicitação de implementação de sistema WMS para requisição de itens na manutenção de equipamentos pneumáticos. Utilização de coletor para leitura dos itens utilizados em cada equipamentos consertado. Importante ressaltar que existem itens utilizados que não são fornecidos pela BINAAR, como</t>
-  </si>
-  <si>
-    <t>37753</t>
-  </si>
-  <si>
-    <t>Compras</t>
-  </si>
-  <si>
-    <t>Integração da maquina - Analise</t>
-  </si>
-  <si>
-    <t>Boa tarde, @Edson João Hammermeister conforme conversamos na reunião, favor seguir com a integração da máquina Cenci, acredito que já esteva conversando com eles. https://documenter.getpostman.com/view/24484248/2sA3kRJPEZ#282fad9d-f4d0-48ff-b7c0-62f4e8fe2ba5 Fico no aguardo do retorno. Att</t>
-  </si>
-  <si>
-    <t>Alan Jonis da Silva</t>
-  </si>
-  <si>
-    <t>Em Análise</t>
-  </si>
-  <si>
-    <t>30069</t>
-  </si>
-  <si>
-    <t>Controle de Importação - integração financeira</t>
-  </si>
-  <si>
-    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
-  </si>
-  <si>
-    <t>Esses relatórios também devem estar disponíveis na aba de relatórios para extração em excel a qualquer momento</t>
-  </si>
-  <si>
-    <t>37749</t>
-  </si>
-  <si>
-    <t>Estorno para itens de saldo fornecedor</t>
-  </si>
-  <si>
-    <t>Boa tarde! Atualmente temos disponível a modalidade saldo fornecedor para os fornecedores Fiedler e Binaar. No entanto, o sistema não disponibiliza a opção de estorno em casos de requisições realizadas de forma indevida. Diante disso, solicitamos a inclusão de uma funcionalidade de estorno para aten</t>
-  </si>
-  <si>
-    <t>Como teremos 3 modelagens as op’s poderão ter quantidades diferentes nas modelagens, validar com o pessoal do APS essa interligação. (copy)</t>
-  </si>
-  <si>
-    <t>35448</t>
-  </si>
-  <si>
-    <t>Solicitação de melhoria no WMS – Pré-lista (EPI)</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
-    <t>37791</t>
-  </si>
-  <si>
-    <t>Solicitação de Análise - Sistema de Custeio</t>
-  </si>
-  <si>
-    <t>Alexandre, bom dia! Gentileza verificar, no cálculo do custeio de fevereiro 2026, a seq. 376MI estava com informação errada de 24 pçs, enquanto que é sequência única.</t>
-  </si>
-  <si>
-    <t>28/04/2026</t>
-  </si>
-  <si>
-    <t>37563</t>
-  </si>
-  <si>
-    <t>Corridas Fora de Liga</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos que esse relatório gere a opção de excel. Com as informações de Forno, Corrida, Liga, Faixa Mínima, Faixa Máxima e mensurado Local onde pode ser adicionado o botão, após colocar as informações de ano e forno abre essa tela, e nessa tela incluir um botão para gerar um excel de t</t>
-  </si>
-  <si>
-    <t>Espectrometria</t>
-  </si>
-  <si>
-    <t>37200</t>
-  </si>
-  <si>
-    <t>Apontamento Escarfa - Apresentacao e acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos da elaboração de um sistema web para o corte escarfa UPR. São duas linhas apontadas por um operador simultaneamente (linha 1 e linha 2), Pra facilitar visual do operador e dinâmica dividir as duas linhas na mesma tela, mas com todos os resultados separados. As sequencias devem se</t>
-  </si>
-  <si>
-    <t>35890</t>
-  </si>
-  <si>
-    <t>Criar API para receber informações do MES para a abertura da SS</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>Tela de Cadastro de Turmas</t>
-  </si>
-  <si>
-    <t>37330</t>
-  </si>
-  <si>
-    <t>MELHORIAS NO APONTAEMNTO LINHA FASE 4 - UPR</t>
-  </si>
-  <si>
-    <t>Boa tarde, Estamos enfrentando uma dificuldade em dividir tempos na linha fase 4 que se encontra hoje em teste. Precisamos que o tempo da peça (sequência) que se encontra finalizada (100% indicado pelo operador) com retoques marcadas pela inspeção próximo a troca de turno, seja somado ao apontamento</t>
-  </si>
-  <si>
-    <t>33631</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - Custos</t>
-  </si>
-  <si>
-    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
-  </si>
-  <si>
-    <t>Automatização DRE Gerencial - Pós fechamento de custos</t>
-  </si>
-  <si>
-    <t>36722</t>
-  </si>
-  <si>
-    <t>Bloco K - Integração dados Altona / Benner.</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Frontend</t>
-  </si>
-  <si>
-    <t>36915</t>
-  </si>
-  <si>
-    <t>SOBREPOSIÇÃO DE ALERTAS</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor verificar a sistemática de alerta de revisão no sistema PCP, pois está havendo sobreposições de comandos no aviso do alerta de revisão: At.te</t>
-  </si>
-  <si>
-    <t>37361</t>
-  </si>
-  <si>
-    <t>Base Histórica da Data de Reconhecimento  de Receita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
-  </si>
-  <si>
-    <t>37190</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
-  </si>
-  <si>
-    <t>Guilherme Ferreira</t>
-  </si>
-  <si>
-    <t>32141</t>
-  </si>
-  <si>
-    <t>Cadastro de Embalagem no CPP (APS)</t>
-  </si>
-  <si>
-    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
-  </si>
-  <si>
-    <t>02/06/2026</t>
-  </si>
-  <si>
-    <t>Implementar Alerta Ordens de serviços com data de programação (já programadas) e não foram executadas</t>
-  </si>
-  <si>
-    <t>37745</t>
-  </si>
-  <si>
-    <t>Sistema de Apontamento corte pó de ferro</t>
-  </si>
-  <si>
-    <t>Bom dia preciso que seja feito algumas alterações e seja adicionado algumas novas funções no sistema de apontamentos dos tablets no pó de ferro. · Adicionar modelo ao lado da sequência. Durante o apontamento e após finalizado é necessário adicionar o modelo correspondente a sequência para o conhecim</t>
-  </si>
-  <si>
-    <t>Amanda Vitoria Aroeira Marinho</t>
-  </si>
-  <si>
-    <t>32133</t>
-  </si>
-  <si>
-    <t>Novo Recurso</t>
-  </si>
-  <si>
-    <t>Automatização planilha comercial - PARTE 2/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
-  </si>
-  <si>
-    <t>Jacson Schneider Movidesk</t>
-  </si>
-  <si>
-    <t>Revisar os campos: data, hora e prazo da proposta</t>
-  </si>
-  <si>
-    <t>36376</t>
-  </si>
-  <si>
-    <t>NOVA PERGUNTA ALERTA DE REVISÃO</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>Fevereiro</t>
-  </si>
-  <si>
-    <t>37863</t>
-  </si>
-  <si>
-    <t>Alteração manual de campanhas</t>
-  </si>
-  <si>
-    <t>Solicito possibilidade de alteração manual nesta tela</t>
-  </si>
-  <si>
-    <t>37774</t>
-  </si>
-  <si>
-    <t>(Oferta/oportunidade - identificação analista de vendas.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prezado, bom dia. O processo que migra as ofertas/oportunidades para o CRM está definindo o ADMINISTRADOR como responsável por todas elas. Isso gera um problema quando o usuário tenta localizar suas próprias ofertas/oportunidades no CRM. A Senior analisou a situação e sugeriu uma forma de contornar </t>
-  </si>
-  <si>
-    <t>38015</t>
-  </si>
-  <si>
-    <t>Inclusão de parâmetro de exportação de notas</t>
-  </si>
-  <si>
-    <t>Bom dia! Peço que na hora de exportar as notas para o sistema do Benner, seja adicionado mais um parâmetro para os produtos, conforme demonstrado abaixo: Esse ajuste já foi feito na tabela [ED_DOCUMENTOITENS], mas precisa ser feito também na [FN_DOCUMENTOLANCOBSAJUSTES].</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>38017</t>
-  </si>
-  <si>
-    <t>Função de Anexo - Recolocar botão para enviar anexo para a calibragem</t>
-  </si>
-  <si>
-    <t>Boa tarde, Chamado já executado, somente abrindo a solicitação para mapeamento da área. Tiago havia executado uma alteração no botão de anexos do equipamento na pagina de baixa de ordens de serviço, e depois descobri que precisávamos manter o antigo botão em funcionamento pois eram documentos enviad</t>
-  </si>
-  <si>
-    <t>Criar estrutura para controlar mais de 01 modelo por placa</t>
-  </si>
-  <si>
-    <t>23/04/2026</t>
-  </si>
-  <si>
-    <t>Consulta para SS e OS em atraso</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>Dashboard de Change Log - Governança de TI</t>
-  </si>
-  <si>
-    <t>Período</t>
-  </si>
-  <si>
-    <t>SPRINT 2026-12</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Tickets corporativos para intranet / Power BI / Excel</t>
-  </si>
-  <si>
-    <t>Total de tickets</t>
-  </si>
-  <si>
-    <t>% dentro do SLA</t>
-  </si>
-  <si>
-    <t>Tempo médio (dias)</t>
-  </si>
-  <si>
-    <t>Áreas atendidas</t>
-  </si>
-  <si>
-    <t>Status final</t>
-  </si>
-  <si>
-    <t>Encerrado</t>
-  </si>
-  <si>
-    <t>Resumo Executivo</t>
-  </si>
-  <si>
-    <t>Tickets por Área</t>
-  </si>
-  <si>
-    <t>Distribuição por Tipo</t>
-  </si>
-  <si>
-    <t>Cumprimento SLA (15 dias)</t>
-  </si>
-  <si>
-    <t>Status Final</t>
-  </si>
-  <si>
-    <t>Tickets por Semana</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Muito Alta</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1650,13 +1713,13 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>34</v>
@@ -1670,40 +1733,40 @@
         <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>34</v>
@@ -1714,22 +1777,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1744,13 +1807,13 @@
         <v>31</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>34</v>
@@ -1761,43 +1824,43 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>34</v>
@@ -1808,43 +1871,43 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>34</v>
@@ -1858,40 +1921,40 @@
         <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>34</v>
@@ -1902,22 +1965,22 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1935,7 +1998,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>26</v>
@@ -1949,43 +2012,43 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>34</v>
@@ -1996,43 +2059,43 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>34</v>
@@ -2043,43 +2106,43 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>34</v>
@@ -2090,43 +2153,43 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>34</v>
@@ -2137,22 +2200,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -2167,13 +2230,13 @@
         <v>31</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>34</v>
@@ -2187,40 +2250,40 @@
         <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>34</v>
@@ -2231,7 +2294,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -2243,10 +2306,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -2261,13 +2324,13 @@
         <v>31</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>34</v>
@@ -2278,22 +2341,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -2308,13 +2371,13 @@
         <v>31</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>34</v>
@@ -2325,43 +2388,43 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>34</v>
@@ -2372,22 +2435,22 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -2405,10 +2468,10 @@
         <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>34</v>
@@ -2419,31 +2482,31 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>31</v>
@@ -2466,22 +2529,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2493,13 +2556,13 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>26</v>
@@ -2513,25 +2576,25 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>21</v>
@@ -2540,13 +2603,13 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>26</v>
@@ -2560,22 +2623,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2593,7 +2656,7 @@
         <v>24</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>26</v>
@@ -2607,43 +2670,43 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>34</v>
@@ -2654,43 +2717,43 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>34</v>
@@ -2701,43 +2764,43 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>34</v>
@@ -2748,22 +2811,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2775,66 +2838,66 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>35</v>
@@ -2842,40 +2905,40 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>26</v>
@@ -2889,43 +2952,43 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>27</v>
@@ -2936,46 +2999,46 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>35</v>
@@ -2983,25 +3046,25 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>21</v>
@@ -3010,45 +3073,45 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -3063,10 +3126,10 @@
         <v>24</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>34</v>
@@ -3077,43 +3140,43 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>34</v>
@@ -3124,31 +3187,31 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>31</v>
@@ -3157,10 +3220,10 @@
         <v>24</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>34</v>
@@ -3171,43 +3234,43 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>34</v>
@@ -3218,40 +3281,40 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>26</v>
@@ -3265,25 +3328,25 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>21</v>
@@ -3298,7 +3361,7 @@
         <v>24</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>26</v>
@@ -3312,40 +3375,40 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>26</v>
@@ -3362,40 +3425,40 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>34</v>
@@ -3406,31 +3469,31 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>31</v>
@@ -3439,7 +3502,7 @@
         <v>24</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>26</v>
@@ -3453,43 +3516,43 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>34</v>
@@ -3500,43 +3563,43 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>34</v>
@@ -3547,40 +3610,40 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
@@ -3597,40 +3660,40 @@
         <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>34</v>
@@ -3641,31 +3704,31 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>31</v>
@@ -3674,7 +3737,7 @@
         <v>24</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>26</v>
@@ -3688,43 +3751,43 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>16</v>
+        <v>197</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>34</v>
@@ -3735,43 +3798,43 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>34</v>
@@ -3782,40 +3845,40 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>26</v>
@@ -3829,31 +3892,31 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>31</v>
@@ -3862,7 +3925,7 @@
         <v>24</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>26</v>
@@ -3879,40 +3942,40 @@
         <v>36</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>34</v>
@@ -3926,40 +3989,40 @@
         <v>36</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>34</v>
@@ -3970,31 +4033,31 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>31</v>
@@ -4017,43 +4080,43 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>34</v>
@@ -4064,43 +4127,43 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>34</v>
@@ -4111,7 +4174,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -4123,10 +4186,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -4158,46 +4221,46 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -4205,25 +4268,25 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>21</v>
@@ -4238,7 +4301,7 @@
         <v>24</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>26</v>
@@ -4252,43 +4315,43 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>34</v>
@@ -4299,22 +4362,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -4326,19 +4389,19 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>28</v>
@@ -4346,43 +4409,43 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>34</v>
@@ -4393,34 +4456,34 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>24</v>
@@ -4432,7 +4495,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>35</v>
@@ -4440,46 +4503,46 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>35</v>
@@ -4487,25 +4550,25 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>21</v>
@@ -4520,7 +4583,7 @@
         <v>24</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>26</v>
@@ -4534,43 +4597,43 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>253</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>34</v>
@@ -4581,40 +4644,40 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>16</v>
+        <v>255</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>26</v>
@@ -4628,43 +4691,43 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>263</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>34</v>
@@ -4675,40 +4738,40 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>246</v>
+        <v>100</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>26</v>
@@ -4722,43 +4785,43 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>34</v>
@@ -4769,43 +4832,43 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>34</v>
@@ -4816,43 +4879,43 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>34</v>
@@ -4866,40 +4929,40 @@
         <v>36</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>34</v>
@@ -4910,25 +4973,25 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>21</v>
@@ -4943,7 +5006,7 @@
         <v>24</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>26</v>
@@ -4957,43 +5020,43 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>265</v>
+        <v>48</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>34</v>
@@ -5004,43 +5067,43 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>34</v>
@@ -5051,43 +5114,43 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>34</v>
@@ -5098,25 +5161,25 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>21</v>
@@ -5125,19 +5188,19 @@
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>292</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>35</v>
@@ -5145,43 +5208,43 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>34</v>
@@ -5192,22 +5255,22 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
@@ -5219,19 +5282,19 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>35</v>
@@ -5239,46 +5302,46 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>35</v>
@@ -5286,43 +5349,43 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>34</v>
@@ -5333,40 +5396,40 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M82" s="2" t="s">
         <v>26</v>
@@ -5380,40 +5443,40 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>26</v>
@@ -5427,7 +5490,7 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>15</v>
+        <v>308</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
@@ -5439,10 +5502,10 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5454,7 +5517,7 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>24</v>
@@ -5466,7 +5529,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>35</v>
@@ -5474,46 +5537,46 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>28</v>
@@ -5521,40 +5584,40 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>26</v>
@@ -5568,43 +5631,43 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>34</v>
@@ -5615,43 +5678,43 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>34</v>
@@ -5662,43 +5725,43 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>34</v>
@@ -5709,43 +5772,43 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>34</v>
@@ -5756,43 +5819,43 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>34</v>
@@ -5803,31 +5866,31 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>31</v>
@@ -5836,10 +5899,10 @@
         <v>24</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>34</v>
@@ -5850,40 +5913,40 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>24</v>
+        <v>175</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M93" s="2" t="s">
         <v>26</v>
@@ -5892,48 +5955,48 @@
         <v>34</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>27</v>
@@ -5944,43 +6007,43 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>27</v>
@@ -5991,43 +6054,43 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>27</v>
@@ -6038,43 +6101,43 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>27</v>
@@ -6088,40 +6151,40 @@
         <v>36</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>332</v>
+        <v>117</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>27</v>
@@ -6132,43 +6195,43 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>334</v>
+        <v>253</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N99" s="2" t="s">
         <v>27</v>
@@ -6190,23 +6253,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="B2" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="D2" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="E2" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6214,16 +6277,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6231,23 +6294,23 @@
         <v>98</v>
       </c>
       <c r="D5" s="5">
-        <v>0.03076923076923077</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>31.31</v>
+        <v>24.95</v>
       </c>
       <c r="J5" s="4">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K22">
         <v>53</v>
@@ -6255,7 +6318,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K23">
         <v>12</v>
@@ -6263,7 +6326,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6294,12 +6357,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="B2">
         <v>98</v>
@@ -6307,41 +6370,41 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.03076923076923077</v>
+        <v>0</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>31.31</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6349,34 +6412,34 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10">
         <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>113</v>
+        <v>374</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N10">
         <v>53</v>
       </c>
       <c r="P10" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="Q10">
         <v>4</v>
@@ -6384,10 +6447,10 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -6396,39 +6459,39 @@
         <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H11">
         <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K11">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="M11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N11">
         <v>21</v>
       </c>
       <c r="P11" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -6440,10 +6503,10 @@
         <v>55</v>
       </c>
       <c r="J12" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="K12">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
         <v>25</v>
@@ -6455,30 +6518,30 @@
         <v>34</v>
       </c>
       <c r="Q12">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="N13">
         <v>4</v>
@@ -6487,44 +6550,50 @@
         <v>27</v>
       </c>
       <c r="Q13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N14">
         <v>12</v>
       </c>
+      <c r="P14" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q14">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M15" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -6532,13 +6601,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M16" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6546,24 +6615,44 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>170</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M17" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
       <c r="D19" s="6" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -6571,150 +6660,174 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
       <c r="D21" s="2" t="s">
-        <v>211</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>56</v>
+        <v>877</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2</v>
+      </c>
       <c r="D22" s="2" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>41</v>
+        <v>877</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
       <c r="D23" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F23" s="2">
-        <v>32</v>
+        <v>877</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
       <c r="D24" s="2" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>32</v>
+        <v>877</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>279</v>
+        <v>107</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>29</v>
+        <v>877</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>280</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>299</v>
+        <v>110</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>29</v>
+        <v>877</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>300</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>17</v>
+        <v>877</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="F28" s="2">
-        <v>17</v>
+        <v>877</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>17</v>
+        <v>877</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>255</v>
+        <v>163</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F30" s="2">
-        <v>17</v>
+        <v>877</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>256</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
